--- a/events/Montemor_2016_WC/Montemor_2016_WC_Results.xlsx
+++ b/events/Montemor_2016_WC/Montemor_2016_WC_Results.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X748"/>
+  <dimension ref="A1:X758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,11 +812,6 @@
           <t>00:05.600</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2677,11 +2672,6 @@
           <t>00:28.552</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>51826</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5232,11 +5222,6 @@
           <t>53048</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>47909</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5827,11 +5812,6 @@
           <t>69299</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6912,11 +6892,6 @@
           <t>00:06.240</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8805,11 +8780,6 @@
           <t>45715</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9160,11 +9130,6 @@
           <t>61242</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10705,11 +10670,6 @@
           <t>69210</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10770,11 +10730,6 @@
           <t>04:52.052</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11185,11 +11140,6 @@
           <t>00:03.068</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>51826</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13210,11 +13160,6 @@
           <t>53048</t>
         </is>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>47909</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13730,11 +13675,6 @@
           <t>69299</t>
         </is>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14735,11 +14675,6 @@
           <t>00:05.252</t>
         </is>
       </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15645,11 +15580,6 @@
           <t>45715</t>
         </is>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -17035,11 +16965,6 @@
           <t>69210</t>
         </is>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -19497,11 +19422,6 @@
           <t>00:08.632</t>
         </is>
       </c>
-      <c r="R267" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -21066,11 +20986,6 @@
           <t>00:12.440</t>
         </is>
       </c>
-      <c r="R289" t="inlineStr">
-        <is>
-          <t>51826</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -21754,11 +21669,6 @@
           <t>69299</t>
         </is>
       </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -23862,11 +23772,6 @@
           <t>61242</t>
         </is>
       </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -24165,11 +24070,6 @@
           <t>45715</t>
         </is>
       </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -29678,11 +29578,6 @@
           <t>00:09.192</t>
         </is>
       </c>
-      <c r="R409" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -32201,11 +32096,6 @@
           <t>00:05.024</t>
         </is>
       </c>
-      <c r="R446" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -32406,11 +32296,6 @@
           <t>00:13.416</t>
         </is>
       </c>
-      <c r="R449" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -34480,11 +34365,6 @@
           <t>61242</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -38280,11 +38160,6 @@
           <t>00:01.692</t>
         </is>
       </c>
-      <c r="R531" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -39390,11 +39265,6 @@
           <t>00:03.808</t>
         </is>
       </c>
-      <c r="R547" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -39665,11 +39535,6 @@
           <t>00:12.896</t>
         </is>
       </c>
-      <c r="R551" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -42585,11 +42450,6 @@
           <t>00:01.328</t>
         </is>
       </c>
-      <c r="R591" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -42940,11 +42800,6 @@
           <t>00:06.960</t>
         </is>
       </c>
-      <c r="R596" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -43223,11 +43078,6 @@
           <t>00:00.856</t>
         </is>
       </c>
-      <c r="R600" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -46493,11 +46343,6 @@
           <t>61242</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -51294,11 +51139,6 @@
           <t>42171</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -52610,11 +52450,6 @@
           <t>02:05.460</t>
         </is>
       </c>
-      <c r="R724" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -52701,7 +52536,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D726" t="n">
@@ -52722,36 +52557,41 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L726" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="M726" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N726" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P726" t="inlineStr">
         <is>
-          <t>24:25.710</t>
+          <t>23:03.590</t>
+        </is>
+      </c>
+      <c r="Q726" t="inlineStr">
+        <is>
+          <t>02:20.000</t>
         </is>
       </c>
       <c r="R726" t="inlineStr">
         <is>
-          <t>42510</t>
+          <t>45021</t>
         </is>
       </c>
     </row>
@@ -52768,7 +52608,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D727" t="n">
@@ -52789,41 +52629,41 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L727" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="M727" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N727" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="P727" t="inlineStr">
         <is>
-          <t>24:40.150</t>
+          <t>23:15.300</t>
         </is>
       </c>
       <c r="Q727" t="inlineStr">
         <is>
-          <t>00:14.440</t>
+          <t>02:31.710</t>
         </is>
       </c>
       <c r="R727" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>52581</t>
         </is>
       </c>
     </row>
@@ -52840,7 +52680,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D728" t="n">
@@ -52861,41 +52701,41 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L728" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="M728" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N728" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="P728" t="inlineStr">
         <is>
-          <t>25:04.980</t>
+          <t>23:16.280</t>
         </is>
       </c>
       <c r="Q728" t="inlineStr">
         <is>
-          <t>00:39.270</t>
+          <t>02:32.690</t>
         </is>
       </c>
       <c r="R728" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>69904</t>
         </is>
       </c>
     </row>
@@ -52912,7 +52752,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D729" t="n">
@@ -52933,41 +52773,41 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>INA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L729" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="M729" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N729" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="P729" t="inlineStr">
         <is>
-          <t>25:25.210</t>
+          <t>23:30.390</t>
         </is>
       </c>
       <c r="Q729" t="inlineStr">
         <is>
-          <t>00:59.500</t>
+          <t>02:46.800</t>
         </is>
       </c>
       <c r="R729" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>61338</t>
         </is>
       </c>
     </row>
@@ -52984,7 +52824,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D730" t="n">
@@ -53005,41 +52845,41 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L730" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M730" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="N730" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="P730" t="inlineStr">
         <is>
-          <t>25:42.160</t>
+          <t>23:31.150</t>
         </is>
       </c>
       <c r="Q730" t="inlineStr">
         <is>
-          <t>01:16.450</t>
+          <t>02:47.560</t>
         </is>
       </c>
       <c r="R730" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>66400</t>
         </is>
       </c>
     </row>
@@ -53056,7 +52896,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D731" t="n">
@@ -53077,41 +52917,41 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L731" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="M731" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="N731" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="P731" t="inlineStr">
         <is>
-          <t>25:47.630</t>
+          <t>23:34.220</t>
         </is>
       </c>
       <c r="Q731" t="inlineStr">
         <is>
-          <t>01:21.920</t>
+          <t>02:50.630</t>
         </is>
       </c>
       <c r="R731" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>52576</t>
         </is>
       </c>
     </row>
@@ -53128,7 +52968,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D732" t="n">
@@ -53149,41 +52989,41 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L732" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M732" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="N732" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="P732" t="inlineStr">
         <is>
-          <t>25:56.060</t>
+          <t>23:58.720</t>
         </is>
       </c>
       <c r="Q732" t="inlineStr">
         <is>
-          <t>01:30.350</t>
+          <t>03:15.130</t>
         </is>
       </c>
       <c r="R732" t="inlineStr">
         <is>
-          <t>63242</t>
+          <t>69006</t>
         </is>
       </c>
     </row>
@@ -53200,7 +53040,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D733" t="n">
@@ -53221,41 +53061,41 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L733" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="M733" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="N733" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="P733" t="inlineStr">
         <is>
-          <t>26:10.170</t>
+          <t>24:14.570</t>
         </is>
       </c>
       <c r="Q733" t="inlineStr">
         <is>
-          <t>01:44.460</t>
+          <t>03:30.980</t>
         </is>
       </c>
       <c r="R733" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>69212</t>
         </is>
       </c>
     </row>
@@ -53272,7 +53112,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D734" t="n">
@@ -53293,7 +53133,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -53303,31 +53143,20 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L734" t="n">
-        <v>42</v>
-      </c>
-      <c r="M734" t="n">
-        <v>9</v>
-      </c>
-      <c r="N734" t="n">
-        <v>9</v>
-      </c>
-      <c r="P734" t="inlineStr">
-        <is>
-          <t>26:55.670</t>
-        </is>
-      </c>
-      <c r="Q734" t="inlineStr">
-        <is>
-          <t>02:29.960</t>
-        </is>
+        <v>20</v>
       </c>
       <c r="R734" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>56241</t>
+        </is>
+      </c>
+      <c r="X734" t="inlineStr">
+        <is>
+          <t>DSQ</t>
         </is>
       </c>
     </row>
@@ -53344,7 +53173,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D735" t="n">
@@ -53365,41 +53194,30 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L735" t="n">
-        <v>32</v>
-      </c>
-      <c r="M735" t="n">
-        <v>10</v>
-      </c>
-      <c r="N735" t="n">
-        <v>10</v>
-      </c>
-      <c r="P735" t="inlineStr">
-        <is>
-          <t>26:56.650</t>
-        </is>
-      </c>
-      <c r="Q735" t="inlineStr">
-        <is>
-          <t>02:30.940</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="R735" t="inlineStr">
         <is>
-          <t>53063</t>
+          <t>35862</t>
+        </is>
+      </c>
+      <c r="X735" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
     </row>
@@ -53442,7 +53260,7 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>INA</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
@@ -53451,22 +53269,22 @@
         </is>
       </c>
       <c r="L736" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M736" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N736" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P736" t="inlineStr">
         <is>
-          <t>27:29.240</t>
-        </is>
-      </c>
-      <c r="Q736" t="inlineStr">
-        <is>
-          <t>03:03.530</t>
+          <t>24:25.710</t>
+        </is>
+      </c>
+      <c r="R736" t="inlineStr">
+        <is>
+          <t>42510</t>
         </is>
       </c>
     </row>
@@ -53509,7 +53327,7 @@
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
@@ -53518,27 +53336,27 @@
         </is>
       </c>
       <c r="L737" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M737" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N737" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P737" t="inlineStr">
         <is>
-          <t>27:58.990</t>
+          <t>24:40.150</t>
         </is>
       </c>
       <c r="Q737" t="inlineStr">
         <is>
-          <t>03:33.280</t>
+          <t>00:14.440</t>
         </is>
       </c>
       <c r="R737" t="inlineStr">
         <is>
-          <t>45015</t>
+          <t>42447</t>
         </is>
       </c>
     </row>
@@ -53581,7 +53399,7 @@
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
@@ -53590,27 +53408,27 @@
         </is>
       </c>
       <c r="L738" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M738" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N738" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P738" t="inlineStr">
         <is>
-          <t>28:03.590</t>
+          <t>25:04.980</t>
         </is>
       </c>
       <c r="Q738" t="inlineStr">
         <is>
-          <t>03:37.880</t>
+          <t>00:39.270</t>
         </is>
       </c>
       <c r="R738" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>41742</t>
         </is>
       </c>
     </row>
@@ -53653,7 +53471,7 @@
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>IRI</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
@@ -53662,16 +53480,27 @@
         </is>
       </c>
       <c r="L739" t="n">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="M739" t="n">
+        <v>4</v>
+      </c>
+      <c r="N739" t="n">
+        <v>4</v>
+      </c>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>25:25.210</t>
+        </is>
+      </c>
+      <c r="Q739" t="inlineStr">
+        <is>
+          <t>00:59.500</t>
+        </is>
       </c>
       <c r="R739" t="inlineStr">
         <is>
-          <t>52758</t>
-        </is>
-      </c>
-      <c r="X739" t="inlineStr">
-        <is>
-          <t>DSQ</t>
+          <t>66401</t>
         </is>
       </c>
     </row>
@@ -53714,7 +53543,7 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>IRI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
@@ -53723,16 +53552,27 @@
         </is>
       </c>
       <c r="L740" t="n">
-        <v>36</v>
+        <v>29</v>
+      </c>
+      <c r="M740" t="n">
+        <v>5</v>
+      </c>
+      <c r="N740" t="n">
+        <v>5</v>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>25:42.160</t>
+        </is>
+      </c>
+      <c r="Q740" t="inlineStr">
+        <is>
+          <t>01:16.450</t>
+        </is>
       </c>
       <c r="R740" t="inlineStr">
         <is>
-          <t>52761</t>
-        </is>
-      </c>
-      <c r="X740" t="inlineStr">
-        <is>
-          <t>DNF</t>
+          <t>48163</t>
         </is>
       </c>
     </row>
@@ -53775,7 +53615,7 @@
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
@@ -53784,23 +53624,34 @@
         </is>
       </c>
       <c r="L741" t="n">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="M741" t="n">
+        <v>6</v>
+      </c>
+      <c r="N741" t="n">
+        <v>6</v>
+      </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>25:47.630</t>
+        </is>
+      </c>
+      <c r="Q741" t="inlineStr">
+        <is>
+          <t>01:21.920</t>
+        </is>
       </c>
       <c r="R741" t="inlineStr">
         <is>
-          <t>42270</t>
-        </is>
-      </c>
-      <c r="X741" t="inlineStr">
-        <is>
-          <t>DNS</t>
+          <t>54736</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -53810,7 +53661,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D742" t="n">
@@ -53831,43 +53682,48 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>17:10:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L742" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M742" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N742" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P742" t="inlineStr">
         <is>
-          <t>23:31.480</t>
+          <t>25:56.060</t>
+        </is>
+      </c>
+      <c r="Q742" t="inlineStr">
+        <is>
+          <t>01:30.350</t>
         </is>
       </c>
       <c r="R742" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>63242</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -53877,7 +53733,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D743" t="n">
@@ -53898,48 +53754,48 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>17:10:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L743" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M743" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N743" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P743" t="inlineStr">
         <is>
-          <t>23:32.470</t>
+          <t>26:10.170</t>
         </is>
       </c>
       <c r="Q743" t="inlineStr">
         <is>
-          <t>00:00.990</t>
+          <t>01:44.460</t>
         </is>
       </c>
       <c r="R743" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>52245</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -53949,7 +53805,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D744" t="n">
@@ -53970,48 +53826,48 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>17:10:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L744" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M744" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N744" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P744" t="inlineStr">
         <is>
-          <t>23:33.450</t>
+          <t>26:55.670</t>
         </is>
       </c>
       <c r="Q744" t="inlineStr">
         <is>
-          <t>00:01.970</t>
+          <t>02:29.960</t>
         </is>
       </c>
       <c r="R744" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>42493</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -54021,7 +53877,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D745" t="n">
@@ -54042,48 +53898,48 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>17:10:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L745" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M745" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N745" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P745" t="inlineStr">
         <is>
-          <t>23:44.500</t>
+          <t>26:56.650</t>
         </is>
       </c>
       <c r="Q745" t="inlineStr">
         <is>
-          <t>00:13.020</t>
+          <t>02:30.940</t>
         </is>
       </c>
       <c r="R745" t="inlineStr">
         <is>
-          <t>61360</t>
+          <t>53063</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -54093,7 +53949,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D746" t="n">
@@ -54114,48 +53970,43 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>17:10:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L746" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="M746" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N746" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P746" t="inlineStr">
         <is>
-          <t>24:58.110</t>
+          <t>27:29.240</t>
         </is>
       </c>
       <c r="Q746" t="inlineStr">
         <is>
-          <t>01:26.630</t>
-        </is>
-      </c>
-      <c r="R746" t="inlineStr">
-        <is>
-          <t>53289</t>
+          <t>03:03.530</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -54165,7 +54016,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D747" t="n">
@@ -54186,48 +54037,48 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>17:10:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L747" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M747" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N747" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P747" t="inlineStr">
         <is>
-          <t>26:28.890</t>
+          <t>27:58.990</t>
         </is>
       </c>
       <c r="Q747" t="inlineStr">
         <is>
-          <t>02:57.410</t>
+          <t>03:33.280</t>
         </is>
       </c>
       <c r="R747" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>45015</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -54237,7 +54088,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D748" t="n">
@@ -54258,28 +54109,710 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L748" t="n">
+        <v>34</v>
+      </c>
+      <c r="M748" t="n">
+        <v>13</v>
+      </c>
+      <c r="N748" t="n">
+        <v>13</v>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>28:03.590</t>
+        </is>
+      </c>
+      <c r="Q748" t="inlineStr">
+        <is>
+          <t>03:37.880</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L749" t="n">
+        <v>38</v>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>52758</t>
+        </is>
+      </c>
+      <c r="X749" t="inlineStr">
+        <is>
+          <t>DSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L750" t="n">
+        <v>36</v>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>52761</t>
+        </is>
+      </c>
+      <c r="X750" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L751" t="n">
+        <v>33</v>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>42270</t>
+        </is>
+      </c>
+      <c r="X751" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
           <t>17:10:00</t>
         </is>
       </c>
-      <c r="I748" t="inlineStr">
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L752" t="n">
+        <v>50</v>
+      </c>
+      <c r="M752" t="n">
+        <v>1</v>
+      </c>
+      <c r="N752" t="n">
+        <v>1</v>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>23:31.480</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>42797</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>17:10:00</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L753" t="n">
+        <v>49</v>
+      </c>
+      <c r="M753" t="n">
+        <v>2</v>
+      </c>
+      <c r="N753" t="n">
+        <v>2</v>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>23:32.470</t>
+        </is>
+      </c>
+      <c r="Q753" t="inlineStr">
+        <is>
+          <t>00:00.990</t>
+        </is>
+      </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>42360</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>17:10:00</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
         <is>
           <t>GER</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr">
+      <c r="K754" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="L748" t="n">
+      <c r="L754" t="n">
+        <v>46</v>
+      </c>
+      <c r="M754" t="n">
+        <v>3</v>
+      </c>
+      <c r="N754" t="n">
+        <v>3</v>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>23:33.450</t>
+        </is>
+      </c>
+      <c r="Q754" t="inlineStr">
+        <is>
+          <t>00:01.970</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>42908</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>17:10:00</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L755" t="n">
+        <v>45</v>
+      </c>
+      <c r="M755" t="n">
+        <v>4</v>
+      </c>
+      <c r="N755" t="n">
+        <v>4</v>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>23:44.500</t>
+        </is>
+      </c>
+      <c r="Q755" t="inlineStr">
+        <is>
+          <t>00:13.020</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>61360</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>17:10:00</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L756" t="n">
+        <v>54</v>
+      </c>
+      <c r="M756" t="n">
+        <v>5</v>
+      </c>
+      <c r="N756" t="n">
+        <v>5</v>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>24:58.110</t>
+        </is>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>01:26.630</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>53289</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>17:10:00</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L757" t="n">
+        <v>53</v>
+      </c>
+      <c r="M757" t="n">
+        <v>6</v>
+      </c>
+      <c r="N757" t="n">
+        <v>6</v>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>26:28.890</t>
+        </is>
+      </c>
+      <c r="Q757" t="inlineStr">
+        <is>
+          <t>02:57.410</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>61755</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>17:10:00</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>GER</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L758" t="n">
         <v>48</v>
       </c>
-      <c r="R748" t="inlineStr">
+      <c r="R758" t="inlineStr">
         <is>
           <t>54680</t>
         </is>
       </c>
-      <c r="X748" t="inlineStr">
+      <c r="X758" t="inlineStr">
         <is>
           <t>DNF</t>
         </is>
@@ -54296,7 +54829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54610,17 +55143,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51924</t>
+          <t>52472</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BLAZEVIC</t>
+          <t>BONDAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -54632,17 +55165,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52472</t>
+          <t>70331</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BONDAR</t>
+          <t>BONITO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -54654,105 +55187,105 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>70331</t>
+          <t>63497</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BONITO</t>
+          <t>BOROWSKA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>63497</t>
+          <t>69299</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOROWSKA</t>
+          <t>BOWKER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>69299</t>
+          <t>61360</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Boróka</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOWKER</t>
+          <t>BRAUN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>61360</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boróka</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BRAUN</t>
+          <t>BRYANT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>35865</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BRYANT</t>
+          <t>BRZEZINSKI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -54764,17 +55297,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35865</t>
+          <t>69212</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRZEZINSKI</t>
+          <t>BURDIAK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -54786,17 +55319,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BURDIAK</t>
+          <t>BURGER</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -54808,17 +55341,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>35296</t>
+          <t>53284</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Boryslav</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BURGER</t>
+          <t>BYZU</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -54830,17 +55363,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>60024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Boryslav</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BYZU</t>
+          <t>CABAÑÍN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -54852,17 +55385,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>60024</t>
+          <t>60029</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CABAÑÍN</t>
+          <t>CAMPO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -54874,17 +55407,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>60029</t>
+          <t>42729</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CAMPO</t>
+          <t>CARRERAS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -54896,78 +55429,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42729</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CARRERAS</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>64652</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Bohdan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>CHABAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>64652</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bohdan</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHABAN</t>
+          <t>CHEN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>52503</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Stephenie</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -54984,39 +55517,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>52503</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stephenie</t>
+          <t>Ryui-Wern</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>CHENG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ryui-Wern</t>
+          <t>Gwanghee</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CHENG</t>
+          <t>CHO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -55028,12 +55561,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gwanghee</t>
+          <t>Jeonghyun</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -55050,17 +55583,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45021</t>
+          <t>70016</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jeonghyun</t>
+          <t>Jisung</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CHO</t>
+          <t>CHOI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -55072,12 +55605,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>70016</t>
+          <t>61291</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jisung</t>
+          <t>Minji</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -55087,19 +55620,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>70014</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Minji</t>
+          <t>Minkyu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -55109,24 +55642,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>70014</t>
+          <t>52261</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Minkyu</t>
+          <t>Youyong</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CHOI</t>
+          <t>CHU</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -55138,17 +55671,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>52261</t>
+          <t>45529</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Youyong</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CHU</t>
+          <t>CLARKE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -55160,17 +55693,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>45529</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLARKE</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -55182,17 +55715,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -55204,61 +55737,61 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>46869</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>COCO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>46869</t>
+          <t>53066</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Stanton</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>COLLINS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>64764</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Stanton</t>
+          <t>António</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COLLINS</t>
+          <t>CONCEIÇÃO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -55270,61 +55803,61 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>64764</t>
+          <t>46831</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>António</t>
+          <t>Isabel</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CONCEIÇÃO</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>46831</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CÁCERES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>42724</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CÁCERES</t>
+          <t>DAL BO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -55336,17 +55869,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DAL BO</t>
+          <t>DE JONGE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -55358,17 +55891,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>42731</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DE JONGE</t>
+          <t>DE TORRES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -55380,17 +55913,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DE TORRES</t>
+          <t>DECORCHEMONT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -55402,61 +55935,61 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>54046</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Nataliia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DECORCHEMONT</t>
+          <t>DOKIIENKO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>54046</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nataliia</t>
+          <t>Igor</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DOKIIENKO</t>
+          <t>DOROFEEV</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Igor</t>
+          <t>Josef</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DOROFEEV</t>
+          <t>DOSTÁL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -55468,39 +56001,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Josef</t>
+          <t>Cathrin</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DOSTÁL</t>
+          <t>DUERR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>70686</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cathrin</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DUERR</t>
+          <t>DÍAZ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -55512,17 +56045,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>70686</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DÍAZ</t>
+          <t>EGAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -55534,12 +56067,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -55549,24 +56082,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>52758</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Seyedkia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EGAN</t>
+          <t>ESKANDANIHOSSEINI</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -55578,17 +56111,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>52758</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Seyedkia</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ESKANDANIHOSSEINI</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -55600,39 +56133,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>36040</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FARRAR-WELLMAN</t>
+          <t>FERNÁNDEZ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>54760</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>FIGUEIRAS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -55644,17 +56177,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>36040</t>
+          <t>61242</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FERNÁNDEZ</t>
+          <t>FITZSIMMONS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -55666,17 +56199,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>54760</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FIGUEIRAS</t>
+          <t>FITZSIMON</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -55688,83 +56221,83 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>61242</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FITZSIMMONS</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Jasmin</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FITZSIMON</t>
+          <t>FRITZ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>66394</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Gandie</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GANDIE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jasmin</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FRITZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -55776,17 +56309,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>66394</t>
+          <t>63242</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gandie</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GANDIE</t>
+          <t>GARRIDO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -55798,17 +56331,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>54844</t>
+          <t>53048</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>María</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GARRO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -55820,17 +56353,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>63242</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GARRIDO</t>
+          <t>GARROTE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -55842,17 +56375,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>53048</t>
+          <t>42908</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>María</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GARRO</t>
+          <t>GEBHARDT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -55864,17 +56397,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>46843</t>
+          <t>61518</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Tibor</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GARROTE</t>
+          <t>GECSÖ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -55886,61 +56419,61 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Wiktor</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GEBHARDT</t>
+          <t>GLAZUNOW</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>61518</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tibor</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GECSÖ</t>
+          <t>GOMES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wiktor</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GLAZUNOW</t>
+          <t>GONZÁLEZ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -55952,39 +56485,39 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GOMES</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>60023</t>
+          <t>63811</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>José</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GONZÁLEZ</t>
+          <t>GÓMEZ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -55996,39 +56529,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Johanna</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>HANDRICK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>63811</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>Mugi</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GÓMEZ</t>
+          <t>HARJITO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -56040,39 +56573,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Johanna</t>
+          <t>Timo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HANDRICK</t>
+          <t>HASELEU</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mugi</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HARJITO</t>
+          <t>HAVEL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -56084,17 +56617,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>42515</t>
+          <t>64475</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timo</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HASELEU</t>
+          <t>HECKER</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -56106,17 +56639,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HAVEL</t>
+          <t>HEFNER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -56128,17 +56661,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>64475</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Asep</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HECKER</t>
+          <t>HIDAYAT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -56150,39 +56683,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>42360</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HEFNER</t>
+          <t>HOGAN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>66400</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Asep</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HIDAYAT</t>
+          <t>HORNSBY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -56194,83 +56727,83 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>56241</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HOGAN</t>
+          <t>HUGHES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>70684</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Antia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HORNSBY</t>
+          <t>JACOME</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>56241</t>
+          <t>54679</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HUGHES</t>
+          <t>JAHN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>70684</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Antia</t>
+          <t>Spela</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JACOME</t>
+          <t>JANIC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -56282,61 +56815,61 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>54679</t>
+          <t>42488</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JAHN</t>
+          <t>JESSOP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>51625</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Spela</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JANIC</t>
+          <t>KACZMAREK</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JESSOP</t>
+          <t>KACZOR</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -56348,17 +56881,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Shawn</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KACZMAREK</t>
+          <t>KAHO'OKELE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -56370,17 +56903,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>42270</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>KAMINSKI</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -56392,61 +56925,61 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>61301</t>
+          <t>45142</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Shawn</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KAHO'OKELE</t>
+          <t>KATRINECZ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Edyta</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KAMINSKI</t>
+          <t>KIERKLA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>45142</t>
+          <t>70017</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Gukjoo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KATRINECZ</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -56458,237 +56991,237 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>70015</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Jiwon</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KERESZTESI</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>45015</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Edyta</t>
+          <t>Taeeun</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KIERKLA</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>70017</t>
+          <t>42512</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Gukjoo</t>
+          <t>Felix</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>KOENIG</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>70015</t>
+          <t>70467</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jiwon</t>
+          <t>Yuliia</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>KOLESNYK</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>45015</t>
+          <t>53054</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Taeeun</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>KOWALD</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>54680</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Felix</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KOENIG</t>
+          <t>KRANKEMANN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>70467</t>
+          <t>69006</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Yuliia</t>
+          <t>Norbert</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KOLESNYK</t>
+          <t>KUCZYNSKI</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>53054</t>
+          <t>35872</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KOWALD</t>
+          <t>KUDLA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>54680</t>
+          <t>53227</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Oleh</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KRANKEMANN</t>
+          <t>KUKHARYK</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>69006</t>
+          <t>53289</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Norbert</t>
+          <t>Liudmyla</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KUCZYNSKI</t>
+          <t>KUKLINOVSKA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KUDLA</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -56700,17 +57233,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>53227</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Oleh</t>
+          <t>Rui</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KUKHARYK</t>
+          <t>LACERDA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -56722,17 +57255,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Liudmyla</t>
+          <t>Francisca</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>KUKLINOVSKA</t>
+          <t>LAIA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -56744,17 +57277,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>61246</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Pierre-Luc</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>LALIBERTE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -56766,17 +57299,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>54675</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rui</t>
+          <t>Felix</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LACERDA</t>
+          <t>LANDES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -56788,17 +57321,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>42486</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Francisca</t>
+          <t>Andreanne</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LAIA</t>
+          <t>LANGLOIS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -56810,39 +57343,39 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>61246</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pierre-Luc</t>
+          <t>Begoña</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LALIBERTE</t>
+          <t>LAZKANO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Felix</t>
+          <t>Aurélien</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LANDES</t>
+          <t>LE GALL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -56854,171 +57387,171 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>42538</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Andreanne</t>
+          <t>Franck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LANGLOIS</t>
+          <t>LE MOEL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>49440</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Begoña</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LAZKANO</t>
+          <t>LECRUBIER</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Aurélien</t>
+          <t>Geraldine</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LE GALL</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>42538</t>
+          <t>45019</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Franck</t>
+          <t>Halin</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LE MOEL</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LECRUBIER</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>54741</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Geraldine</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>LEMKE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>45019</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Halin</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>LEONARD</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Dongyin</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -57030,39 +57563,39 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>54741</t>
+          <t>42663</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LEMKE</t>
+          <t>LISIECKA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>54129</t>
+          <t>64778</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LEONARD</t>
+          <t>LOPES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -57074,39 +57607,39 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>52199</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Dongyin</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LUBNIEWSKI</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Martyna</t>
+          <t>Noémi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LISIECKA</t>
+          <t>LUCZ</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -57118,17 +57651,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>64778</t>
+          <t>65582</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LOPES</t>
+          <t>LUENGO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -57140,39 +57673,39 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>53226</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Liudmyla</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LUBNIEWSKI</t>
+          <t>LUZAN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Noémi</t>
+          <t>Eszter</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LUCZ</t>
+          <t>MALCSINER</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -57184,17 +57717,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>65582</t>
+          <t>70412</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LUENGO</t>
+          <t>MARINOV</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -57206,83 +57739,83 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>66393</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Liudmyla</t>
+          <t>Marjuki</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LUZAN</t>
+          <t>MARJUKI</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>45131</t>
+          <t>72649</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Eszter</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MALCSINER</t>
+          <t>MARTÍN</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>70412</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MARINOV</t>
+          <t>MAYER</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>66393</t>
+          <t>35867</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Marjuki</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MARJUKI</t>
+          <t>MAZUR</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -57294,61 +57827,61 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>72649</t>
+          <t>69449</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Tabea</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MARTÍN</t>
+          <t>MEDERT</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Spen</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MAYER</t>
+          <t>MEHUE</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MAZUR</t>
+          <t>MILLER</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -57360,17 +57893,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>47619</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Marty</t>
+          <t>Rubén</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MCDOWELL</t>
+          <t>MILLÁN</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -57382,39 +57915,39 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tabea</t>
+          <t>Adel</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MEDERT</t>
+          <t>MOJALLALIMOGHADAM</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>66404</t>
+          <t>70332</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Spen</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MEHUE</t>
+          <t>MOREIRA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -57426,39 +57959,39 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>54853</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MILLER</t>
+          <t>MORISON</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>47619</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rubén</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MILLÁN</t>
+          <t>MORNEAU</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -57470,17 +58003,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>52787</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Adel</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MOJALLALIMOGHADAM</t>
+          <t>MORTIMER</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -57492,17 +58025,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>70332</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Mohssine</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MOREIRA</t>
+          <t>MOUTAHIR</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -57514,39 +58047,39 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>54853</t>
+          <t>53052</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MORISON</t>
+          <t>MUELLER</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>61338</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MORNEAU</t>
+          <t>MULLICAN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -57558,39 +58091,39 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MORTIMER</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>52575</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Mohssine</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MOUTAHIR</t>
+          <t>NASIMAN</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -57602,17 +58135,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Yul</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MUELLER</t>
+          <t>OELTZE</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -57624,17 +58157,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>61338</t>
+          <t>52761</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MULLICAN</t>
+          <t>OJAGHI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -57646,39 +58179,39 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>46835</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>André</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NASIMAN</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -57690,17 +58223,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>42510</t>
+          <t>52581</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Yul</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>OELTZE</t>
+          <t>OOI</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -57712,17 +58245,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>63757</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OJAGHI</t>
+          <t>ORIYÉS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -57734,39 +58267,39 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>47295</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>OUZANDE</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>46835</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>André</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -57778,17 +58311,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>OOI</t>
+          <t>PAROL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -57800,17 +58333,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>63757</t>
+          <t>63899</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ORIYÉS</t>
+          <t>PEDRERO</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -57822,17 +58355,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Szabina</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>OUZANDE</t>
+          <t>PILLER</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -57844,17 +58377,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -57866,17 +58399,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>54759</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Igor</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PAROL</t>
+          <t>PINHO</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -57888,17 +58421,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>63899</t>
+          <t>51814</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Ilya</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PEDRERO</t>
+          <t>PODPOLNYY</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -57910,39 +58443,39 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>46832</t>
+          <t>61255</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Pierre-Luc</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PEDRUELO</t>
+          <t>POULIN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Szabina</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PILLER</t>
+          <t>PULAWSKA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -57954,17 +58487,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>PUTTO</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -57976,61 +58509,61 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>69027</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Igor</t>
+          <t>Qiurong</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PINHO</t>
+          <t>QIAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>51814</t>
+          <t>70685</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ilya</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PODPOLNYY</t>
+          <t>RAMAL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>61255</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Pierre-Luc</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>POULIN</t>
+          <t>REGORIUS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -58042,61 +58575,61 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>69904</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Maizir</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PULAWSKA</t>
+          <t>RIYONDRA</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PUTTO</t>
+          <t>RODRIGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Qiurong</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>QIAN</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -58108,39 +58641,39 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>70685</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>RAMAL</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>64487</t>
+          <t>53063</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>REGORIUS</t>
+          <t>ROSS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -58152,17 +58685,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>69904</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Maizir</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>RIYONDRA</t>
+          <t>ROSS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -58174,39 +58707,39 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>57977</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Pelayo</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>RODRIGUES</t>
+          <t>ROZA</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>56986</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -58218,61 +58751,61 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>63808</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>RÍOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>53063</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Deborah</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ROSS</t>
+          <t>SAW</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>46808</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Conrad</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ROSS</t>
+          <t>SCHEIBNER</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -58284,61 +58817,61 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>69145</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Pelayo</t>
+          <t>Madeline</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ROZA</t>
+          <t>SCHMIDT</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>61392</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>SCOTT</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>63808</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>RÍOS</t>
+          <t>SEAH</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -58350,39 +58883,39 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Deborah</t>
+          <t>Dongjin</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SAW</t>
+          <t>SHIN</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Conrad</t>
+          <t>Jevgenij</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SCHEIBNER</t>
+          <t>SHUKLIN</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -58394,39 +58927,39 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Madeline</t>
+          <t>Emanuel</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SCHMIDT</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>61392</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SCOTT</t>
+          <t>SIMART</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -58438,17 +58971,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>52506</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Fanni</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SEAH</t>
+          <t>SIMÁN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -58460,17 +58993,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>35869</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dongjin</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SHIN</t>
+          <t>SLOMINSKI</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -58482,39 +59015,39 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>61754</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Jevgenij</t>
+          <t>Sze</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SHUKLIN</t>
+          <t>SOH</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Emanuel</t>
+          <t>Kuongho</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>SONG</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -58526,17 +59059,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SIMART</t>
+          <t>STABNO</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -58548,17 +59081,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>60184</t>
+          <t>63894</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fanni</t>
+          <t>Magda</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>SIMÁN</t>
+          <t>STANNY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -58570,17 +59103,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Xinchang</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>SLOMINSKI</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -58592,39 +59125,39 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>61754</t>
+          <t>66399</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Sze</t>
+          <t>Sutrisno</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SOH</t>
+          <t>SUTRISNO</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>45017</t>
+          <t>66397</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Kuongho</t>
+          <t>Dedi</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SONG</t>
+          <t>SUYATNO</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -58636,17 +59169,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>42596</t>
+          <t>63493</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Patryk</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>STABNO</t>
+          <t>SWITALSKI</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -58658,17 +59191,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Magda</t>
+          <t>Ágnes</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>STANNY</t>
+          <t>SZABÓ</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -58680,17 +59213,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>52260</t>
+          <t>69300</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Xinchang</t>
+          <t>Ferenc</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>SZEKSZARDI</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -58702,39 +59235,39 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>66399</t>
+          <t>60064</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Sutrisno</t>
+          <t>Anett</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SUTRISNO</t>
+          <t>SZILÁGYI</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Dedi</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SUYATNO</t>
+          <t>TAME</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -58746,61 +59279,61 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>88740</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Patryk</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SWITALSKI</t>
+          <t>TANKO</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>45143</t>
+          <t>42494</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Ágnes</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SZABÓ</t>
+          <t>TARDIOLI</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>69300</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ferenc</t>
+          <t>Anwar</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SZEKSZARDI</t>
+          <t>TARRA</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -58812,39 +59345,39 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>60064</t>
+          <t>42414</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Anett</t>
+          <t>Tiago</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SZILÁGYI</t>
+          <t>TAVARES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Zi</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>TAME</t>
+          <t>TAY</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -58856,39 +59389,39 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>88740</t>
+          <t>52576</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>TANKO</t>
+          <t>TEO</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>52580</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Mervyn</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TARDIOLI</t>
+          <t>TOH</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -58900,17 +59433,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Anwar</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>TARRA</t>
+          <t>TREFIL</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -58922,39 +59455,39 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>42414</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Tiago</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TAVARES</t>
+          <t>TULEU</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Zi</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>TAY</t>
+          <t>VALLEJO</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -58966,17 +59499,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>52576</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>TEO</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -58988,39 +59521,39 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>52580</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mervyn</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>TOH</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>54773</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>TREFIL</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -59032,61 +59565,61 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>42493</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>TULEU</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>54850</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>VALLEJO</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Tilen</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VIDOVIC</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -59098,39 +59631,39 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>70333</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Edgar</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>VIEIRA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>54773</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Rubén</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>VOISARD</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -59142,17 +59675,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>57980</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VÁZQUEZ</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -59164,17 +59697,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -59186,17 +59719,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tilen</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>VIDOVIC</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -59208,17 +59741,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>70333</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Edgar</t>
+          <t>Longkui</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>VIEIRA</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -59230,17 +59763,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>42726</t>
+          <t>41742</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Rubén</t>
+          <t>Riwei</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>VOISARD</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -59252,17 +59785,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>57980</t>
+          <t>63861</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Yufei</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>VÁZQUEZ</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -59274,39 +59807,39 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>54677</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>WEISE</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -59318,61 +59851,61 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Longkui</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>69210</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Riwei</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>WRIGHT</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>63861</t>
+          <t>68864</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Yufei</t>
+          <t>Lida</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>XIE</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -59384,17 +59917,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>52166</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Song</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>XING</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -59406,61 +59939,61 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>54677</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Caihong</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>WEISE</t>
+          <t>XU</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>52586</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>WOJNAROWSKA</t>
+          <t>YAP</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>47415</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Haisai</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -59472,39 +60005,39 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>69210</t>
+          <t>35920</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>WRIGHT</t>
+          <t>ŠPICAR</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>68864</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Lida</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>XIE</t>
+          <t>ŠTERBA</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -59516,152 +60049,20 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Song</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>XING</t>
+          <t>ŠVÁB</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>52198</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Caihong</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>XU</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>52586</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>YAP</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>61024</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Haisai</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>35920</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Jakub</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>ŠPICAR</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>35776</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>ŠTERBA</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>35550</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Filip</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>ŠVÁB</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Montemor_2016_WC/Montemor_2016_WC_Results.xlsx
+++ b/events/Montemor_2016_WC/Montemor_2016_WC_Results.xlsx
@@ -812,6 +812,11 @@
           <t>00:05.600</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2672,6 +2677,11 @@
           <t>00:28.552</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>51826</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5222,6 +5232,11 @@
           <t>53048</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5812,6 +5827,11 @@
           <t>69299</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6892,6 +6912,11 @@
           <t>00:06.240</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8780,6 +8805,11 @@
           <t>45715</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9130,6 +9160,11 @@
           <t>61242</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10670,6 +10705,11 @@
           <t>69210</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10730,6 +10770,11 @@
           <t>04:52.052</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11140,6 +11185,11 @@
           <t>00:03.068</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>51826</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13160,6 +13210,11 @@
           <t>53048</t>
         </is>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13675,6 +13730,11 @@
           <t>69299</t>
         </is>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14675,6 +14735,11 @@
           <t>00:05.252</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15580,6 +15645,11 @@
           <t>45715</t>
         </is>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -16965,6 +17035,11 @@
           <t>69210</t>
         </is>
       </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -19422,6 +19497,11 @@
           <t>00:08.632</t>
         </is>
       </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -20986,6 +21066,11 @@
           <t>00:12.440</t>
         </is>
       </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>51826</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -21669,6 +21754,11 @@
           <t>69299</t>
         </is>
       </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -23772,6 +23862,11 @@
           <t>61242</t>
         </is>
       </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -24070,6 +24165,11 @@
           <t>45715</t>
         </is>
       </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -29578,6 +29678,11 @@
           <t>00:09.192</t>
         </is>
       </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -32096,6 +32201,11 @@
           <t>00:05.024</t>
         </is>
       </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -32296,6 +32406,11 @@
           <t>00:13.416</t>
         </is>
       </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -34365,6 +34480,11 @@
           <t>61242</t>
         </is>
       </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -38160,6 +38280,11 @@
           <t>00:01.692</t>
         </is>
       </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -39265,6 +39390,11 @@
           <t>00:03.808</t>
         </is>
       </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -39535,6 +39665,11 @@
           <t>00:12.896</t>
         </is>
       </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -42450,6 +42585,11 @@
           <t>00:01.328</t>
         </is>
       </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -42800,6 +42940,11 @@
           <t>00:06.960</t>
         </is>
       </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -43078,6 +43223,11 @@
           <t>00:00.856</t>
         </is>
       </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -46343,6 +46493,11 @@
           <t>61242</t>
         </is>
       </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -51139,6 +51294,11 @@
           <t>42171</t>
         </is>
       </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -52448,6 +52608,11 @@
       <c r="Q724" t="inlineStr">
         <is>
           <t>02:05.460</t>
+        </is>
+      </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>51924</t>
         </is>
       </c>
     </row>
@@ -54829,7 +54994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60068,6 +60233,138 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>PEDRUELO</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>51826</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Marty</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>MCDOWELL</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>KERESZTESI</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>WOOD</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>47792</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Ariel</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>FARRAR-WELLMAN</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>BLAZEVIC</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Montemor_2016_WC/Montemor_2016_WC_Results.xlsx
+++ b/events/Montemor_2016_WC/Montemor_2016_WC_Results.xlsx
@@ -3787,6 +3787,11 @@
           <t>00:04.012</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4567,6 +4572,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8950,6 +8960,11 @@
           <t>00:13.648</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>54773</t>
@@ -9230,6 +9245,11 @@
           <t>00:05.456</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>53227</t>
@@ -9305,6 +9325,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10560,6 +10585,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12430,6 +12460,11 @@
           <t>00:02.868</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13065,6 +13100,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15495,6 +15535,11 @@
           <t>03:35.964</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>53227</t>
@@ -16230,6 +16275,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16445,6 +16495,11 @@
           <t>00:05.700</t>
         </is>
       </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>54773</t>
@@ -16890,6 +16945,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -18767,6 +18827,11 @@
           <t>00:05.236</t>
         </is>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>54773</t>
@@ -20356,6 +20421,11 @@
           <t>00:12.444</t>
         </is>
       </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -23646,6 +23716,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -23713,6 +23788,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -24088,6 +24168,11 @@
           <t>00:03.496</t>
         </is>
       </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S330" t="inlineStr">
         <is>
           <t>53227</t>
@@ -24545,6 +24630,11 @@
           <t>54770</t>
         </is>
       </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -25608,6 +25698,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -27603,6 +27698,11 @@
           <t>00:00.096</t>
         </is>
       </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -30573,6 +30673,11 @@
           <t>00:02.512</t>
         </is>
       </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -30972,6 +31077,11 @@
       <c r="L428" t="n">
         <v>1</v>
       </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>54083</t>
+        </is>
+      </c>
       <c r="X428" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -31996,6 +32106,11 @@
       <c r="L443" t="n">
         <v>8</v>
       </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
       <c r="X443" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -32271,6 +32386,11 @@
           <t>00:05.344</t>
         </is>
       </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -32460,6 +32580,11 @@
       <c r="L450" t="n">
         <v>5</v>
       </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>36391</t>
+        </is>
+      </c>
       <c r="X450" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -33165,6 +33290,11 @@
           <t>54770</t>
         </is>
       </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -34060,6 +34190,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="U472" t="inlineStr">
         <is>
           <t>36450</t>
@@ -34725,6 +34860,11 @@
           <t>54773</t>
         </is>
       </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
       <c r="U480" t="inlineStr">
         <is>
           <t>70332</t>
@@ -36205,6 +36345,11 @@
           <t>00:41.408</t>
         </is>
       </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -39460,6 +39605,11 @@
           <t>00:06.940</t>
         </is>
       </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -40910,6 +41060,11 @@
           <t>54773</t>
         </is>
       </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
       <c r="U568" t="inlineStr">
         <is>
           <t>70332</t>
@@ -42729,6 +42884,11 @@
           <t>00:04.424</t>
         </is>
       </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -45075,6 +45235,11 @@
           <t>00:39.188</t>
         </is>
       </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -46098,6 +46263,11 @@
           <t>54770</t>
         </is>
       </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -46662,6 +46832,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="U647" t="inlineStr">
         <is>
           <t>36450</t>
@@ -47082,6 +47257,11 @@
           <t>70331</t>
         </is>
       </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
       <c r="T652" t="inlineStr">
         <is>
           <t>54773</t>
@@ -48157,6 +48337,11 @@
           <t>00:04.880</t>
         </is>
       </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -48875,6 +49060,11 @@
           <t>69027</t>
         </is>
       </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
       <c r="U676" t="inlineStr">
         <is>
           <t>52198</t>
@@ -49044,6 +49234,11 @@
           <t>61291</t>
         </is>
       </c>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
       <c r="U678" t="inlineStr">
         <is>
           <t>70017</t>
@@ -49419,6 +49614,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -52109,6 +52309,11 @@
       <c r="Q717" t="inlineStr">
         <is>
           <t>01:10.660</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>46407</t>
         </is>
       </c>
     </row>
@@ -54994,7 +55199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60365,6 +60570,248 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>36391</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Bridgitte</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>HARTLEY</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>PORTELA</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Shahou</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>NASERI</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>54083</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Arsen</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SLIWINSKI</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sun Ja</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>CAMEIRA</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Ji</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>WANG</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
